--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel-28/back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Back_Summary.xlsx
@@ -454,28 +454,23 @@
           <t>Unit 7</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
       <c r="C2" t="n">
-        <v>16.83809</v>
+        <v>17.18685</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68178</v>
+        <v>16.43577</v>
       </c>
       <c r="E2" t="n">
-        <v>16.7773</v>
+        <v>16.80602</v>
       </c>
       <c r="F2" t="n">
-        <v>43.13894</v>
+        <v>42.79376</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04963</v>
+        <v>0.05068</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84642</v>
+        <v>1.83034</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +480,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.61603</v>
+        <v>17.00512</v>
       </c>
       <c r="D3" t="n">
-        <v>16.85468</v>
+        <v>16.79342</v>
       </c>
       <c r="E3" t="n">
-        <v>16.58464</v>
+        <v>16.98242</v>
       </c>
       <c r="F3" t="n">
-        <v>42.35806</v>
+        <v>41.62726</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05029</v>
+        <v>0.05137</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84347</v>
+        <v>1.82165</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +505,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.59993</v>
+        <v>17.17426</v>
       </c>
       <c r="D4" t="n">
-        <v>16.83925</v>
+        <v>16.93589</v>
       </c>
       <c r="E4" t="n">
-        <v>16.77493</v>
+        <v>17.07803</v>
       </c>
       <c r="F4" t="n">
-        <v>43.31014</v>
+        <v>41.8881</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05134</v>
+        <v>0.0512</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82545</v>
+        <v>1.78785</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +530,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.70039</v>
+        <v>17.0593</v>
       </c>
       <c r="D5" t="n">
-        <v>16.59552</v>
+        <v>16.82889</v>
       </c>
       <c r="E5" t="n">
-        <v>16.96806</v>
+        <v>17.02373</v>
       </c>
       <c r="F5" t="n">
-        <v>42.93254</v>
+        <v>41.85114</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05137</v>
+        <v>0.05061</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81364</v>
+        <v>1.81863</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +555,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.06091</v>
+        <v>17.28158</v>
       </c>
       <c r="D6" t="n">
-        <v>16.76528</v>
+        <v>16.56929</v>
       </c>
       <c r="E6" t="n">
-        <v>16.84044</v>
+        <v>17.14506</v>
       </c>
       <c r="F6" t="n">
-        <v>42.44416</v>
+        <v>42.86517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05214</v>
+        <v>0.0509</v>
       </c>
       <c r="H6" t="n">
-        <v>1.81042</v>
+        <v>1.78963</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +580,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.78658</v>
+        <v>17.04317</v>
       </c>
       <c r="D7" t="n">
-        <v>16.8074</v>
+        <v>16.47313</v>
       </c>
       <c r="E7" t="n">
-        <v>16.67465</v>
+        <v>16.72691</v>
       </c>
       <c r="F7" t="n">
-        <v>42.68935</v>
+        <v>42.6205</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05</v>
+        <v>0.0505</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8003</v>
+        <v>1.8143</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +605,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.1163</v>
+        <v>16.87942</v>
       </c>
       <c r="D8" t="n">
-        <v>16.67538</v>
+        <v>16.67459</v>
       </c>
       <c r="E8" t="n">
-        <v>17.10659</v>
+        <v>16.78258</v>
       </c>
       <c r="F8" t="n">
-        <v>43.01252</v>
+        <v>42.73218</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05071</v>
+        <v>0.0511</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84166</v>
+        <v>1.82165</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +630,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.19692</v>
+        <v>16.98224</v>
       </c>
       <c r="D9" t="n">
-        <v>16.75402</v>
+        <v>16.55012</v>
       </c>
       <c r="E9" t="n">
-        <v>16.76983</v>
+        <v>16.64293</v>
       </c>
       <c r="F9" t="n">
-        <v>42.69005</v>
+        <v>42.69944</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05138</v>
+        <v>0.05187</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81654</v>
+        <v>1.84663</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +655,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.69371</v>
+        <v>16.91103</v>
       </c>
       <c r="D10" t="n">
-        <v>16.43184</v>
+        <v>16.59505</v>
       </c>
       <c r="E10" t="n">
-        <v>16.93742</v>
+        <v>16.61906</v>
       </c>
       <c r="F10" t="n">
-        <v>43.06889</v>
+        <v>43.4395</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05055</v>
+        <v>0.05092</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83064</v>
+        <v>1.82547</v>
       </c>
     </row>
     <row r="11">
@@ -696,12 +691,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Radius</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Space</t>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -713,8 +713,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>Pad 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>16.67925</v>
+      </c>
+      <c r="D12" t="n">
+        <v>16.50899</v>
+      </c>
+      <c r="E12" t="n">
+        <v>16.66093</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42.94026</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.05076</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.88397</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +741,24 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>16.85006</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.64979</v>
+      </c>
+      <c r="E13" t="n">
+        <v>16.76396</v>
+      </c>
+      <c r="F13" t="n">
+        <v>43.24766</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.04981</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.83654</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +766,24 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>17.04098</v>
+      </c>
+      <c r="D14" t="n">
+        <v>16.78614</v>
+      </c>
+      <c r="E14" t="n">
+        <v>17.00338</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42.65054</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.05044</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.83403</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +791,24 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>17.06237</v>
+      </c>
+      <c r="D15" t="n">
+        <v>16.34547</v>
+      </c>
+      <c r="E15" t="n">
+        <v>16.89332</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42.56878</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0511</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.82402</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +816,24 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>16.9816</v>
+      </c>
+      <c r="D16" t="n">
+        <v>16.45977</v>
+      </c>
+      <c r="E16" t="n">
+        <v>16.81675</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42.14336</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.81267</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +841,24 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>16.72213</v>
+      </c>
+      <c r="D17" t="n">
+        <v>16.25368</v>
+      </c>
+      <c r="E17" t="n">
+        <v>16.71295</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42.50496</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.05025</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.82736</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +866,24 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>17.10458</v>
+      </c>
+      <c r="D18" t="n">
+        <v>16.63775</v>
+      </c>
+      <c r="E18" t="n">
+        <v>17.06201</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42.37506</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.05031</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.80388</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,12 +891,48 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>16.90056</v>
+      </c>
+      <c r="D19" t="n">
+        <v>16.57779</v>
+      </c>
+      <c r="E19" t="n">
+        <v>16.73055</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42.50658</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.05004</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.81585</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.08966</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.49413</v>
+      </c>
+      <c r="E20" t="n">
+        <v>16.95109</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42.42391</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.05104</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.80227</v>
       </c>
     </row>
   </sheetData>
